--- a/data/trans_bre/P11_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 12,47</t>
+          <t>3,38; 12,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 19,93</t>
+          <t>10,09; 19,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 17,14</t>
+          <t>7,29; 17,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,87</t>
+          <t>4,26; 13,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 62,6</t>
+          <t>13,9; 61,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,31; 115,18</t>
+          <t>47,79; 117,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,8; 94,94</t>
+          <t>32,24; 94,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,83; 49,53</t>
+          <t>12,65; 48,64</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 15,26</t>
+          <t>7,13; 14,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,58</t>
+          <t>6,72; 15,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,51</t>
+          <t>7,84; 15,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,95; 28,23</t>
+          <t>12,24; 28,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 109,19</t>
+          <t>40,2; 103,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,14; 77,11</t>
+          <t>29,74; 80,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 89,88</t>
+          <t>37,96; 91,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,74; 257,55</t>
+          <t>49,5; 279,0</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 20,81</t>
+          <t>11,05; 20,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 18,98</t>
+          <t>10,37; 19,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,56</t>
+          <t>5,18; 13,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 48,03</t>
+          <t>4,21; 52,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,96; 118,85</t>
+          <t>50,15; 121,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,14; 167,11</t>
+          <t>67,17; 167,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,36; 86,71</t>
+          <t>26,37; 91,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,37; 218,68</t>
+          <t>16,65; 213,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 13,8</t>
+          <t>6,34; 13,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,28</t>
+          <t>6,03; 14,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,5</t>
+          <t>5,03; 12,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,69</t>
+          <t>1,03; 13,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,6; 92,59</t>
+          <t>33,56; 89,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,92; 74,06</t>
+          <t>25,63; 73,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,0; 78,97</t>
+          <t>25,61; 80,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 51,12</t>
+          <t>3,55; 51,9</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,1</t>
+          <t>8,76; 13,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,65</t>
+          <t>10,55; 14,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,34</t>
+          <t>8,2; 12,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 25,86</t>
+          <t>10,11; 29,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,65; 76,52</t>
+          <t>45,35; 75,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,66; 81,58</t>
+          <t>53,55; 84,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,65; 70,47</t>
+          <t>41,74; 73,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,78; 118,44</t>
+          <t>36,94; 126,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P11_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>8,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,18</t>
+          <t>3,45; 12,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,09; 19,91</t>
+          <t>10,36; 20,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 17,1</t>
+          <t>7,03; 16,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,55</t>
+          <t>4,01; 13,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 61,56</t>
+          <t>14,54; 63,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,79; 117,21</t>
+          <t>47,19; 117,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,24; 94,36</t>
+          <t>31,3; 91,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,65; 48,64</t>
+          <t>11,83; 48,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,68</t>
+          <t>13,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,58</t>
+          <t>6,94; 14,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,09</t>
+          <t>7,29; 14,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,48</t>
+          <t>8,05; 15,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 28,81</t>
+          <t>9,49; 17,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 103,6</t>
+          <t>40,01; 104,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 80,58</t>
+          <t>32,25; 78,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,96; 91,16</t>
+          <t>40,61; 93,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,5; 279,0</t>
+          <t>35,43; 79,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,35</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 20,72</t>
+          <t>10,15; 20,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 19,24</t>
+          <t>10,69; 19,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,87</t>
+          <t>4,85; 13,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 52,23</t>
+          <t>2,47; 11,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,15; 121,99</t>
+          <t>45,87; 118,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,17; 167,84</t>
+          <t>71,07; 168,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 91,07</t>
+          <t>24,94; 90,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,65; 213,36</t>
+          <t>9,27; 53,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,94</t>
+          <t>6,65; 13,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,14</t>
+          <t>6,11; 14,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,81</t>
+          <t>5,3; 12,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 13,94</t>
+          <t>8,46; 15,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,56; 89,89</t>
+          <t>33,27; 90,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 73,65</t>
+          <t>26,11; 73,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 80,16</t>
+          <t>25,72; 77,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 51,9</t>
+          <t>27,93; 61,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,33</t>
+          <t>10,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,15</t>
+          <t>9,0; 13,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,83</t>
+          <t>10,37; 14,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,56</t>
+          <t>8,04; 12,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 29,18</t>
+          <t>8,53; 12,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,35; 75,93</t>
+          <t>46,29; 75,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,55; 84,54</t>
+          <t>51,41; 80,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,74; 73,05</t>
+          <t>41,15; 68,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 126,25</t>
+          <t>30,74; 50,05</t>
         </is>
       </c>
     </row>
